--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486826_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486826_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9307</v>
+        <v>0.3933</v>
       </c>
       <c r="E2" t="n">
-        <v>4.926</v>
+        <v>2.7611</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.9953</v>
+        <v>-2.3678</v>
       </c>
       <c r="G2" t="n">
         <v>0.0862</v>
@@ -610,13 +610,13 @@
         <v>0.5792</v>
       </c>
       <c r="S2" t="n">
-        <v>4.7439</v>
+        <v>2.2065</v>
       </c>
       <c r="T2" t="n">
-        <v>3.5574</v>
+        <v>1.3925</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1865</v>
+        <v>0.8141</v>
       </c>
       <c r="V2" t="n">
         <v>-1.5133</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.7086</v>
+        <v>-0.7156</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.3462</v>
+        <v>-0.9808</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6375999999999999</v>
+        <v>0.2652</v>
       </c>
       <c r="G3" t="n">
         <v>-1.1403</v>
@@ -688,13 +688,13 @@
         <v>1.3515</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5242</v>
+        <v>0.5172</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3866</v>
+        <v>-0.0212</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9109</v>
+        <v>0.5384</v>
       </c>
       <c r="V3" t="n">
         <v>-0.2856</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. COULIBALY</t>
+          <t>M. CRUJEIRAS MOREIRAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.1078</v>
+        <v>-1.1199</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6526999999999999</v>
+        <v>-1.5855</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.7605</v>
+        <v>0.4656</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.6303</v>
+        <v>-0.2068</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8346</v>
+        <v>-0.6272</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.4649</v>
+        <v>0.4205</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1015</v>
+        <v>-0.351</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6282</v>
+        <v>-0.351</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5266999999999999</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7318</v>
+        <v>0.1442</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2065</v>
+        <v>-0.2763</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.9382</v>
+        <v>0.4205</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.7723</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9654</v>
+        <v>-1.1585</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1931</v>
+        <v>0.7723</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5225</v>
+        <v>-0.2413</v>
       </c>
       <c r="T4" t="n">
-        <v>1.5166</v>
+        <v>-0.076</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0059</v>
+        <v>-0.1653</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.2277</v>
+        <v>-0.2856</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2277</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.4444</v>
+        <v>-1.5257</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.5804</v>
+        <v>-1.8355</v>
       </c>
       <c r="F5" t="n">
-        <v>0.136</v>
+        <v>0.3098</v>
       </c>
       <c r="G5" t="n">
         <v>1.0326</v>
@@ -844,13 +844,13 @@
         <v>0.3862</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2261</v>
+        <v>0.1449</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4136</v>
+        <v>0.1585</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1874</v>
+        <v>-0.0136</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. CRUJEIRAS MOREIRAS</t>
+          <t>K. TSHIMANGA ZOLA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.6288</v>
+        <v>-1.8782</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.8957</v>
+        <v>-1.0489</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2669</v>
+        <v>-0.8294</v>
       </c>
       <c r="G6" t="n">
+        <v>-1.0769</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.5795</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-0.4974</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.08210000000000001</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.0414</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.0407</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-1.159</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-0.6209</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-0.5381</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-0.9654</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-0.9654</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
         <v>-0.2068</v>
       </c>
-      <c r="H6" t="n">
-        <v>-0.6272</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.4205</v>
-      </c>
-      <c r="J6" t="n">
-        <v>-0.351</v>
-      </c>
-      <c r="K6" t="n">
-        <v>-0.351</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.1442</v>
-      </c>
-      <c r="N6" t="n">
-        <v>-0.2763</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.4205</v>
-      </c>
-      <c r="P6" t="n">
-        <v>-0.3862</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>-1.1585</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.7723</v>
-      </c>
-      <c r="S6" t="n">
-        <v>-0.7502</v>
-      </c>
       <c r="T6" t="n">
-        <v>-0.3863</v>
+        <v>-0.1655</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.364</v>
+        <v>-0.0413</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2856</v>
+        <v>0.3709</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2856</v>
+        <v>0.3709</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. TSHIMANGA ZOLA</t>
+          <t>B. COULIBALY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.8534</v>
+        <v>-2.0579</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.0489</v>
+        <v>-0.2229</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8046</v>
+        <v>-1.835</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.0769</v>
+        <v>-0.6303</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5795</v>
+        <v>0.8346</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4974</v>
+        <v>-1.4649</v>
       </c>
       <c r="J7" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.1015</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0414</v>
+        <v>0.6282</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0407</v>
+        <v>-0.5266999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.159</v>
+        <v>-0.7318</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6209</v>
+        <v>0.2065</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5381</v>
+        <v>-0.9382</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9654</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.1931</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.182</v>
+        <v>0.5724</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1655</v>
+        <v>0.641</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0164</v>
+        <v>-0.06859999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3709</v>
+        <v>-1.2277</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3709</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="8">
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.8779</v>
+        <v>-2.147</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.5114</v>
+        <v>-1.7805</v>
       </c>
       <c r="F8" t="n">
         <v>-0.3665</v>
@@ -1078,10 +1078,10 @@
         <v>0.5792</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0551</v>
+        <v>0.6758</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8554</v>
+        <v>-0.1245</v>
       </c>
       <c r="U8" t="n">
         <v>0.8003</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. ALONSO LANTIGUA</t>
+          <t>A. GUERRA LOZANO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.0002</v>
+        <v>-3.6632</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.1652</v>
+        <v>-3.0191</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8351</v>
+        <v>-0.6441</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.2696</v>
+        <v>-5.2545</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.345</v>
+        <v>0.2546</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9246</v>
+        <v>-5.5092</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2276</v>
+        <v>-2.8324</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3451</v>
+        <v>0.5314</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.1175</v>
+        <v>-3.3637</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.4972</v>
+        <v>-2.4222</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6901</v>
+        <v>-0.2767</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8071</v>
+        <v>-2.1454</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.3169</v>
+        <v>0.9654</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.8962</v>
+        <v>-0.1931</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5792</v>
+        <v>1.1585</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4137</v>
+        <v>0.2551</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4966</v>
+        <v>0.0063</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0829</v>
+        <v>0.2487</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.3709</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.3709</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. PEREZ GALVAN</t>
+          <t>A. ALONSO LANTIGUA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.3435</v>
+        <v>-3.6692</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2913</v>
+        <v>-2.9583</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.0523</v>
+        <v>-0.7109</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.206</v>
+        <v>-1.2696</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6078</v>
+        <v>-0.345</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8138</v>
+        <v>-0.9246</v>
       </c>
       <c r="J10" t="n">
-        <v>2.416</v>
+        <v>0.2276</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5396</v>
+        <v>0.3451</v>
       </c>
       <c r="L10" t="n">
-        <v>1.8764</v>
+        <v>-0.1175</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.622</v>
+        <v>-1.4972</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0682</v>
+        <v>-0.6901</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.6903</v>
+        <v>-0.8071</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.7031</v>
+        <v>-2.3169</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.8616</v>
+        <v>-2.8962</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1585</v>
+        <v>0.5792</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2646</v>
+        <v>-0.0827</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1313</v>
+        <v>-0.2898</v>
       </c>
       <c r="U10" t="n">
-        <v>0.8667</v>
+        <v>0.2071</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.1698</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.4554</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. GUERRA LOZANO</t>
+          <t>A. PEREZ GALVAN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.4079</v>
+        <v>-4.5065</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.2671</v>
+        <v>-1.3053</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1408</v>
+        <v>-3.2013</v>
       </c>
       <c r="G11" t="n">
-        <v>-5.2545</v>
+        <v>-0.206</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2546</v>
+        <v>0.6078</v>
       </c>
       <c r="I11" t="n">
-        <v>-5.5092</v>
+        <v>-0.8138</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.8324</v>
+        <v>2.416</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5314</v>
+        <v>0.5396</v>
       </c>
       <c r="L11" t="n">
-        <v>-3.3637</v>
+        <v>1.8764</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.4222</v>
+        <v>-2.622</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2767</v>
+        <v>0.0682</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.1454</v>
+        <v>-2.6903</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9654</v>
+        <v>-2.7031</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.1931</v>
+        <v>-3.8616</v>
       </c>
       <c r="R11" t="n">
         <v>1.1585</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4896</v>
+        <v>0.5724</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.2417</v>
+        <v>-0.1453</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2479</v>
+        <v>0.7177</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3709</v>
+        <v>-2.1698</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X11" t="n">
-        <v>0.3709</v>
+        <v>-2.4554</v>
       </c>
     </row>
     <row r="12">
@@ -1345,31 +1345,31 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-21.4418</v>
+        <v>-20.8899</v>
       </c>
       <c r="E12" t="n">
-        <v>-12.5275</v>
+        <v>-11.9757</v>
       </c>
       <c r="F12" t="n">
-        <v>-8.9146</v>
+        <v>-8.914399999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-10.2061</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6901999999999999</v>
+        <v>0.6901999999999997</v>
       </c>
       <c r="I12" t="n">
         <v>-10.8964</v>
       </c>
       <c r="J12" t="n">
-        <v>2.9064</v>
+        <v>2.906400000000001</v>
       </c>
       <c r="K12" t="n">
         <v>3.1093</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.2029000000000001</v>
+        <v>-0.2028999999999999</v>
       </c>
       <c r="M12" t="n">
         <v>-13.1125</v>
@@ -1387,13 +1387,13 @@
         <v>-18.3425</v>
       </c>
       <c r="R12" t="n">
-        <v>6.7577</v>
+        <v>6.757700000000001</v>
       </c>
       <c r="S12" t="n">
-        <v>3.8615</v>
+        <v>4.4135</v>
       </c>
       <c r="T12" t="n">
-        <v>0.8242</v>
+        <v>1.376</v>
       </c>
       <c r="U12" t="n">
         <v>3.0375</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.8519</v>
+        <v>5.5898</v>
       </c>
       <c r="E13" t="n">
-        <v>2.3567</v>
+        <v>2.4601</v>
       </c>
       <c r="F13" t="n">
-        <v>2.4952</v>
+        <v>3.1297</v>
       </c>
       <c r="G13" t="n">
         <v>2.5113</v>
@@ -1468,13 +1468,13 @@
         <v>2.7031</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9104</v>
+        <v>-0.1725</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1936</v>
+        <v>-0.0901</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7169</v>
+        <v>-0.0824</v>
       </c>
       <c r="V13" t="n">
         <v>1.5133</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.1356</v>
+        <v>3.3313</v>
       </c>
       <c r="E14" t="n">
-        <v>3.2292</v>
+        <v>3.436</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0936</v>
+        <v>-0.1047</v>
       </c>
       <c r="G14" t="n">
         <v>2.6691</v>
@@ -1546,13 +1546,13 @@
         <v>2.1239</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9542</v>
+        <v>-0.7585</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1036</v>
+        <v>-0.8968</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1494</v>
+        <v>0.1383</v>
       </c>
       <c r="V14" t="n">
         <v>1.2277</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. THIAW</t>
+          <t>M. MELERO JAREÑO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.8867</v>
+        <v>2.9306</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0325</v>
+        <v>1.566</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8541</v>
+        <v>1.3646</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7541</v>
+        <v>1.3099</v>
       </c>
       <c r="H15" t="n">
-        <v>1.0684</v>
+        <v>-0.6004</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3143</v>
+        <v>1.9102</v>
       </c>
       <c r="J15" t="n">
-        <v>1.9623</v>
+        <v>1.711</v>
       </c>
       <c r="K15" t="n">
-        <v>1.7588</v>
+        <v>0.3658</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2035</v>
+        <v>1.3451</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.2082</v>
+        <v>-0.4011</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6904</v>
+        <v>-0.9661999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5178</v>
+        <v>0.5651</v>
       </c>
       <c r="P15" t="n">
-        <v>2.3169</v>
+        <v>0.9654</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3169</v>
+        <v>1.9308</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2138</v>
+        <v>-0.5724</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4684</v>
+        <v>-0.4072</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7454</v>
+        <v>-0.1651</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.3982</v>
+        <v>1.2277</v>
       </c>
       <c r="W15" t="n">
-        <v>-1.3982</v>
+        <v>1.2277</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. MELERO JAREÑO</t>
+          <t>E. QUIJADA GARCÍA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.67</v>
+        <v>2.4599</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2558</v>
+        <v>0.3629</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4142</v>
+        <v>2.0971</v>
       </c>
       <c r="G16" t="n">
-        <v>1.3099</v>
+        <v>1.9278</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.6004</v>
+        <v>-0.152</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9102</v>
+        <v>2.0798</v>
       </c>
       <c r="J16" t="n">
-        <v>1.711</v>
+        <v>0.8182</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3658</v>
+        <v>-0.5653</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3451</v>
+        <v>1.3835</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4011</v>
+        <v>1.1096</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9661999999999999</v>
+        <v>0.4134</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5651</v>
+        <v>0.6962</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9654</v>
+        <v>1.7377</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9308</v>
+        <v>1.7377</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.833</v>
+        <v>-0.6344</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7175</v>
+        <v>-0.4553</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1155</v>
+        <v>-0.179</v>
       </c>
       <c r="V16" t="n">
-        <v>1.2277</v>
+        <v>-0.5712</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4883</v>
+        <v>2.1242</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4622</v>
+        <v>1.0485</v>
       </c>
       <c r="F17" t="n">
-        <v>1.026</v>
+        <v>1.0757</v>
       </c>
       <c r="G17" t="n">
         <v>2.4553</v>
@@ -1780,13 +1780,13 @@
         <v>0.5792</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4191</v>
+        <v>0.0551</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5239</v>
+        <v>0.1102</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1048</v>
+        <v>-0.0551</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. QUIJADA GARCÍA</t>
+          <t>B. BAILLO HERNÁNDEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.9799</v>
+        <v>2.0188</v>
       </c>
       <c r="E18" t="n">
-        <v>0.156</v>
+        <v>1.2192</v>
       </c>
       <c r="F18" t="n">
-        <v>1.8239</v>
+        <v>0.7996</v>
       </c>
       <c r="G18" t="n">
-        <v>1.9278</v>
+        <v>1.6948</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.152</v>
+        <v>0.2412</v>
       </c>
       <c r="I18" t="n">
-        <v>2.0798</v>
+        <v>1.4536</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8182</v>
+        <v>1.4056</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5653</v>
+        <v>0.1035</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3835</v>
+        <v>1.3022</v>
       </c>
       <c r="M18" t="n">
-        <v>1.1096</v>
+        <v>0.2892</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4134</v>
+        <v>0.1377</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6962</v>
+        <v>0.1514</v>
       </c>
       <c r="P18" t="n">
-        <v>1.7377</v>
+        <v>0.7723</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7377</v>
+        <v>0.7723</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1144</v>
+        <v>-0.4483</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6622</v>
+        <v>-0.1864</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4522</v>
+        <v>-0.2619</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.5712</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.5712</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. BAILLO HERNÁNDEZ</t>
+          <t>M. THIAW</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.5348</v>
+        <v>1.804</v>
       </c>
       <c r="E19" t="n">
-        <v>0.909</v>
+        <v>0.3086</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6258</v>
+        <v>1.4954</v>
       </c>
       <c r="G19" t="n">
-        <v>1.6948</v>
+        <v>0.7541</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2412</v>
+        <v>1.0684</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4536</v>
+        <v>-0.3143</v>
       </c>
       <c r="J19" t="n">
-        <v>1.4056</v>
+        <v>1.9623</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1035</v>
+        <v>1.7588</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3022</v>
+        <v>0.2035</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2892</v>
+        <v>-1.2082</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1377</v>
+        <v>-0.6904</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1514</v>
+        <v>-0.5178</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7723</v>
+        <v>2.3169</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7723</v>
+        <v>2.3169</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9323</v>
+        <v>0.1311</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4966</v>
+        <v>-0.2556</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4357</v>
+        <v>0.3866</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.3982</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-1.3982</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.4901</v>
+        <v>1.0364</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7065</v>
+        <v>0.1893</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7836</v>
+        <v>0.847</v>
       </c>
       <c r="G20" t="n">
         <v>-0.6036</v>
@@ -2014,13 +2014,13 @@
         <v>2.1239</v>
       </c>
       <c r="S20" t="n">
-        <v>0.364</v>
+        <v>-0.0897</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4959</v>
+        <v>-0.0212</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1319</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="V20" t="n">
         <v>0.5712</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.0655</v>
+        <v>0.8998</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7822</v>
+        <v>-0.5754</v>
       </c>
       <c r="F21" t="n">
-        <v>1.8477</v>
+        <v>1.4752</v>
       </c>
       <c r="G21" t="n">
         <v>-1.7622</v>
@@ -2092,13 +2092,13 @@
         <v>1.7377</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1377</v>
+        <v>-0.3034</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5795</v>
+        <v>-0.3726</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4418</v>
+        <v>0.0693</v>
       </c>
       <c r="V21" t="n">
         <v>1.2277</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.6608000000000001</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4112</v>
+        <v>-1.1009</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7504</v>
+        <v>1.0373</v>
       </c>
       <c r="G22" t="n">
         <v>-0.7503</v>
@@ -2170,13 +2170,13 @@
         <v>2.3169</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9764</v>
+        <v>-0.3793</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7727000000000001</v>
+        <v>-0.4624</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2038</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="V22" t="n">
         <v>-0.2856</v>
@@ -2203,19 +2203,19 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>21.442</v>
+        <v>22.1311</v>
       </c>
       <c r="E23" t="n">
-        <v>8.9145</v>
+        <v>8.914300000000003</v>
       </c>
       <c r="F23" t="n">
-        <v>12.5273</v>
+        <v>13.2169</v>
       </c>
       <c r="G23" t="n">
         <v>10.2062</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.6904000000000003</v>
+        <v>-0.6904000000000008</v>
       </c>
       <c r="I23" t="n">
         <v>10.8965</v>
@@ -2230,7 +2230,7 @@
         <v>10.6934</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.906299999999999</v>
+        <v>-2.9063</v>
       </c>
       <c r="N23" t="n">
         <v>-3.1094</v>
@@ -2248,19 +2248,19 @@
         <v>18.3424</v>
       </c>
       <c r="S23" t="n">
-        <v>-3.8615</v>
+        <v>-3.1723</v>
       </c>
       <c r="T23" t="n">
-        <v>-3.0375</v>
+        <v>-3.0374</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8242000000000003</v>
+        <v>-0.1347</v>
       </c>
       <c r="V23" t="n">
         <v>3.5126</v>
       </c>
       <c r="W23" t="n">
-        <v>5.597099999999999</v>
+        <v>5.597100000000001</v>
       </c>
       <c r="X23" t="n">
         <v>-2.0845</v>
